--- a/data/trans_dic/P38C-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Estudios-trans_dic.xlsx
@@ -514,7 +514,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,11; 90,58</t>
+          <t>86,08; 90,51</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,18; 91,51</t>
+          <t>86,25; 91,56</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,79; 94,36</t>
+          <t>90,96; 94,6</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89,91; 94,79</t>
+          <t>90,25; 94,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,37; 92,19</t>
+          <t>89,5; 92,21</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,67; 92,94</t>
+          <t>89,65; 93,05</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>77,22; 80,94</t>
+          <t>77,42; 81,09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48,68; 78,12</t>
+          <t>47,52; 78,3</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,07; 87,19</t>
+          <t>84,12; 87,35</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74,78; 87,39</t>
+          <t>74,08; 87,48</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,13; 83,68</t>
+          <t>81,16; 83,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>63,73; 81,79</t>
+          <t>61,62; 81,72</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,93; 83,86</t>
+          <t>76,57; 83,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,72; 86,24</t>
+          <t>77,69; 86,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,09; 86,25</t>
+          <t>80,08; 86,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>86,07; 91,29</t>
+          <t>85,89; 91,13</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79,61; 84,14</t>
+          <t>79,48; 84,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>82,79; 87,86</t>
+          <t>83,1; 87,85</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,04; 82,84</t>
+          <t>80,18; 82,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>57,66; 81,07</t>
+          <t>58,18; 81,03</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,25; 88,54</t>
+          <t>86,35; 88,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>79,69; 88,87</t>
+          <t>80,4; 88,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,61; 85,43</t>
+          <t>83,6; 85,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,75; 84,3</t>
+          <t>70,81; 84,29</t>
         </is>
       </c>
     </row>
@@ -945,7 +945,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población a la que le han medido los niveles de glucosal por prescripción médica</t>
+          <t>Población a la que le han medido los niveles de glucosal por prescripción médica (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>645074; 678560</t>
+          <t>644842; 678074</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>443775; 471200</t>
+          <t>444145; 471492</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>899428; 934726</t>
+          <t>901109; 937143</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>678600; 715486</t>
+          <t>681174; 716098</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1554804; 1603855</t>
+          <t>1557121; 1604246</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1138613; 1180105</t>
+          <t>1138265; 1181497</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1581564; 1657792</t>
+          <t>1585696; 1660842</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1114125; 1788101</t>
+          <t>1087568; 1792086</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1663506; 1725127</t>
+          <t>1664451; 1728267</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1668283; 1949538</t>
+          <t>1652653; 1951745</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3266912; 3369775</t>
+          <t>3268006; 3366571</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2880510; 3696945</t>
+          <t>2785313; 3693465</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>418460; 456195</t>
+          <t>416522; 455162</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>502525; 557631</t>
+          <t>502388; 556555</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>437366; 470995</t>
+          <t>437303; 473478</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>568475; 602969</t>
+          <t>567284; 601857</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>867786; 917132</t>
+          <t>866368; 919668</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1082156; 1148450</t>
+          <t>1086127; 1148322</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2674405; 2767854</t>
+          <t>2678986; 2767863</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1989667; 2797227</t>
+          <t>2007303; 2795816</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3032037; 3112320</t>
+          <t>3035496; 3113241</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2905660; 3240253</t>
+          <t>2931475; 3232091</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5732513; 5857657</t>
+          <t>5731862; 5853724</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5020796; 5982340</t>
+          <t>5025060; 5981505</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P38C-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P38C-Estudios-trans_dic.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>89,21%</t>
+          <t>86,84%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -609,7 +609,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93,16%</t>
+          <t>93,6%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -619,7 +619,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>91,56%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -632,32 +632,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>86,08; 90,51</t>
+          <t>85,92; 90,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>86,25; 91,56</t>
+          <t>83,47; 89,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90,96; 94,6</t>
+          <t>91,11; 94,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90,25; 94,88</t>
+          <t>91,7; 95,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>89,5; 92,21</t>
+          <t>89,46; 92,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>89,65; 93,05</t>
+          <t>89,12; 92,34</t>
         </is>
       </c>
     </row>
@@ -679,7 +679,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>69,17%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,98%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>76,1%</t>
+          <t>79,55%</t>
         </is>
       </c>
     </row>
@@ -712,32 +712,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>77,42; 81,09</t>
+          <t>77,22; 80,97</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>47,52; 78,3</t>
+          <t>73,93; 78,5</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>84,12; 87,35</t>
+          <t>84,04; 87,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>74,08; 87,48</t>
+          <t>81,32; 84,74</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>81,16; 83,6</t>
+          <t>81,22; 83,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>61,62; 81,72</t>
+          <t>78,0; 80,93</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>89,13%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -779,7 +779,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>85,72%</t>
+          <t>86,3%</t>
         </is>
       </c>
     </row>
@@ -792,32 +792,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>76,57; 83,67</t>
+          <t>76,47; 83,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>77,69; 86,07</t>
+          <t>79,83; 86,14</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>80,08; 86,7</t>
+          <t>80,09; 86,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>85,89; 91,13</t>
+          <t>86,57; 91,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>79,48; 84,37</t>
+          <t>79,64; 84,27</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>83,1; 87,85</t>
+          <t>84,19; 88,41</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>74,67%</t>
+          <t>79,41%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,54%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>80,64%</t>
+          <t>83,07%</t>
         </is>
       </c>
     </row>
@@ -872,32 +872,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>80,18; 82,84</t>
+          <t>79,76; 82,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>58,18; 81,03</t>
+          <t>77,58; 81,16</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>86,35; 88,56</t>
+          <t>86,19; 88,57</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>80,4; 88,64</t>
+          <t>85,42; 87,64</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>83,6; 85,37</t>
+          <t>83,74; 85,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,81; 84,29</t>
+          <t>81,92; 84,0</t>
         </is>
       </c>
     </row>
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>459392</t>
+          <t>502378</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -1078,7 +1078,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>703160</t>
+          <t>768079</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1088,7 +1088,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1162553</t>
+          <t>1270457</t>
         </is>
       </c>
     </row>
@@ -1101,32 +1101,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>644842; 678074</t>
+          <t>643629; 678703</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>444145; 471492</t>
+          <t>482889; 519503</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>901109; 937143</t>
+          <t>902567; 934181</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>681174; 716098</t>
+          <t>752514; 780286</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1557121; 1604246</t>
+          <t>1556451; 1605567</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1138265; 1181497</t>
+          <t>1246871; 1291962</t>
         </is>
       </c>
     </row>
@@ -1186,7 +1186,7 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1583209</t>
+          <t>1698933</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1856529</t>
+          <t>1794036</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>3439739</t>
+          <t>3492969</t>
         </is>
       </c>
     </row>
@@ -1219,32 +1219,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1585696; 1660842</t>
+          <t>1581557; 1658374</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1087568; 1792086</t>
+          <t>1648006; 1749889</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1664451; 1728267</t>
+          <t>1662905; 1727057</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1652653; 1951745</t>
+          <t>1758084; 1832065</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3268006; 3366571</t>
+          <t>3270402; 3363465</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2785313; 3693465</t>
+          <t>3425251; 3553633</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>533745</t>
+          <t>593292</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>586721</t>
+          <t>654979</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1120466</t>
+          <t>1248271</t>
         </is>
       </c>
     </row>
@@ -1337,32 +1337,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>416522; 455162</t>
+          <t>415951; 456187</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>502388; 556555</t>
+          <t>568025; 612969</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>437303; 473478</t>
+          <t>437337; 470798</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>567284; 601857</t>
+          <t>636153; 669874</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>866368; 919668</t>
+          <t>868119; 918598</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1086127; 1148322</t>
+          <t>1217841; 1278866</t>
         </is>
       </c>
     </row>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>2576347</t>
+          <t>2794603</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3146410</t>
+          <t>3217094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1442,7 +1442,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5722758</t>
+          <t>6011697</t>
         </is>
       </c>
     </row>
@@ -1455,32 +1455,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2678986; 2767863</t>
+          <t>2665123; 2764715</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2007303; 2795816</t>
+          <t>2730383; 2856140</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>3035496; 3113241</t>
+          <t>3029995; 3113558</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2931475; 3232091</t>
+          <t>3175454; 3258199</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5731862; 5853724</t>
+          <t>5741869; 5862262</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5025060; 5981505</t>
+          <t>5928397; 6078942</t>
         </is>
       </c>
     </row>
